--- a/all reports/MVR.xlsx
+++ b/all reports/MVR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC63CE45-AD54-4A8B-945E-7BDDBA2EC683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2483805C-BBEA-4ADB-8560-95FFAE675459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -592,6 +592,45 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -615,45 +654,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -950,93 +950,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="31" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
     </row>
     <row r="2" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="38" t="s">
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
     </row>
     <row r="3" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="38" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
     </row>
     <row r="4" spans="1:13" s="3" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="37" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="47" t="s">
+      <c r="E4" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47" t="s">
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="49" t="s">
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="41" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="3" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="42"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="46"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="38"/>
       <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
@@ -1064,7 +1064,7 @@
       <c r="L5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="50"/>
+      <c r="M5" s="42"/>
     </row>
     <row r="6" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="7">
@@ -1966,11 +1966,11 @@
       <c r="M55" s="20"/>
     </row>
     <row r="56" spans="1:13" s="25" customFormat="1" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="30" t="s">
+      <c r="A56" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="B56" s="31"/>
-      <c r="C56" s="32"/>
+      <c r="B56" s="44"/>
+      <c r="C56" s="45"/>
       <c r="D56" s="21"/>
       <c r="E56" s="22"/>
       <c r="F56" s="22"/>
@@ -1986,11 +1986,11 @@
       <c r="A57" s="26"/>
     </row>
     <row r="58" spans="1:13" ht="26.5" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A58" s="33" t="s">
+      <c r="A58" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="B58" s="34"/>
-      <c r="C58" s="35"/>
+      <c r="B58" s="47"/>
+      <c r="C58" s="48"/>
       <c r="D58" s="22"/>
       <c r="E58" s="22"/>
       <c r="F58" s="22"/>
@@ -2005,9 +2005,9 @@
       <c r="A59" s="26"/>
     </row>
     <row r="60" spans="1:13" ht="26" x14ac:dyDescent="0.6">
-      <c r="A60" s="36"/>
-      <c r="B60" s="36"/>
-      <c r="C60" s="36"/>
+      <c r="A60" s="49"/>
+      <c r="B60" s="49"/>
+      <c r="C60" s="49"/>
       <c r="D60" s="29"/>
       <c r="E60" s="29"/>
       <c r="F60" s="29"/>
@@ -2089,6 +2089,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="I2:M2"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="I3:M3"/>
@@ -2098,11 +2103,6 @@
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="I4:L4"/>
     <mergeCell ref="M4:M5"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="I2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2128,91 +2128,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="31" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
     </row>
     <row r="2" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
     </row>
     <row r="3" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="38" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
     </row>
     <row r="4" spans="1:13" s="3" customFormat="1" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="37" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="47" t="s">
+      <c r="E4" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47" t="s">
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="49" t="s">
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="41" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="3" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="42"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="46"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="38"/>
       <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
@@ -2240,7 +2240,7 @@
       <c r="L5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="50"/>
+      <c r="M5" s="42"/>
     </row>
     <row r="6" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="7">
@@ -2602,11 +2602,11 @@
       <c r="M25" s="20"/>
     </row>
     <row r="26" spans="1:13" s="25" customFormat="1" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="32"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="45"/>
       <c r="D26" s="21"/>
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
@@ -2622,11 +2622,11 @@
       <c r="A27" s="26"/>
     </row>
     <row r="28" spans="1:13" ht="26.5" thickBot="1" x14ac:dyDescent="0.65">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="35"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="48"/>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
